--- a/module-8/Discussion 8.1 Tables.xlsx
+++ b/module-8/Discussion 8.1 Tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Bob/csd/CSD-310/module-8/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C463DC4-C576-2745-8929-E42DE536B41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70AB7010-4E96-6E45-9A37-427667133E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2780" yWindow="1500" windowWidth="28040" windowHeight="17440" xr2:uid="{A0DF4D82-07A3-204C-9A40-EA93A14E40B5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="17">
   <si>
     <t>Table A: Customers</t>
   </si>
@@ -697,16 +697,16 @@
         <v>15</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" t="s">
-        <v>15</v>
+        <v>5</v>
+      </c>
+      <c r="I20">
+        <v>103</v>
       </c>
       <c r="J20" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -722,17 +722,17 @@
       <c r="D21" t="s">
         <v>12</v>
       </c>
-      <c r="G21">
-        <v>3</v>
+      <c r="G21" t="s">
+        <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I21">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -746,18 +746,6 @@
         <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22">
-        <v>4</v>
-      </c>
-      <c r="H22" t="s">
-        <v>6</v>
-      </c>
-      <c r="I22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" t="s">
         <v>15</v>
       </c>
     </row>
